--- a/resultados/metricas_uni_2020.xlsx
+++ b/resultados/metricas_uni_2020.xlsx
@@ -481,10 +481,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>1586597489.564344</v>
+        <v>1411436552.306663</v>
       </c>
       <c r="C7">
-        <v>0.1057216332415558</v>
+        <v>0.09587727192395802</v>
       </c>
     </row>
     <row r="8" spans="1:3">
